--- a/Templates/water-quality-analysis/test-template-gb.xlsx
+++ b/Templates/water-quality-analysis/test-template-gb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nussdore\Documents\GitHub\WWS-standard-methods\Templates\water-quality-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913D8A18-3A34-4D31-B682-959A6ACB08A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68B221E-01B2-43D7-89D4-1938D0A4029E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample-DateTime" sheetId="21" r:id="rId1"/>
@@ -18,30 +18,18 @@
     <sheet name="Labels-Lab" sheetId="7" r:id="rId3"/>
     <sheet name="DS-Filter Weight" sheetId="18" r:id="rId4"/>
     <sheet name="DS-Bottle Numbers" sheetId="16" r:id="rId5"/>
-    <sheet name="DS-ISCO Bottle Weight" sheetId="17" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="210">
   <si>
     <t>Analysis</t>
   </si>
@@ -64,9 +52,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Sample ID</t>
-  </si>
-  <si>
     <t>(30mL/125mL Bottles)</t>
   </si>
   <si>
@@ -79,9 +64,6 @@
     <t>(any method deviations that could affect the data)</t>
   </si>
   <si>
-    <t>ISCO Bottle Weights</t>
-  </si>
-  <si>
     <t>Filter Weights</t>
   </si>
   <si>
@@ -94,85 +76,589 @@
     <t>Post-Weight</t>
   </si>
   <si>
-    <t>ISCO Bottle (g)</t>
-  </si>
-  <si>
     <t>Sample Name</t>
   </si>
   <si>
     <t>Field Sample ID</t>
   </si>
   <si>
+    <t>Bottle Number</t>
+  </si>
+  <si>
     <t>Lab Sample ID</t>
   </si>
   <si>
-    <t>Time (HHMM)</t>
-  </si>
-  <si>
-    <t>Date (YYYYMMDD)</t>
+    <t>BDRK_R0018</t>
   </si>
   <si>
     <t>B01M</t>
   </si>
   <si>
+    <t>20260727</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>BDRK_R0016</t>
+  </si>
+  <si>
     <t>B02H</t>
   </si>
   <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>BDRK_R0009</t>
+  </si>
+  <si>
     <t>B03H</t>
   </si>
   <si>
+    <t>1020</t>
+  </si>
+  <si>
+    <t>BDRK_R0020</t>
+  </si>
+  <si>
     <t>B04M</t>
   </si>
   <si>
+    <t>1030</t>
+  </si>
+  <si>
+    <t>BDRK_R0019</t>
+  </si>
+  <si>
     <t>B05H</t>
   </si>
   <si>
+    <t>1040</t>
+  </si>
+  <si>
+    <t>BDRK_R0003</t>
+  </si>
+  <si>
     <t>B06H</t>
   </si>
   <si>
+    <t>1050</t>
+  </si>
+  <si>
+    <t>BDRK_R0007</t>
+  </si>
+  <si>
     <t>B07H</t>
   </si>
   <si>
+    <t>1060</t>
+  </si>
+  <si>
+    <t>BDRK_R0013</t>
+  </si>
+  <si>
     <t>B08M</t>
   </si>
   <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>BDRK_R0014</t>
+  </si>
+  <si>
     <t>B09H</t>
   </si>
   <si>
+    <t>1080</t>
+  </si>
+  <si>
+    <t>BDRK_R0010</t>
+  </si>
+  <si>
     <t>B10M</t>
   </si>
   <si>
+    <t>1090</t>
+  </si>
+  <si>
+    <t>BDRK_R0005</t>
+  </si>
+  <si>
     <t>U11H</t>
   </si>
   <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>BDRK_R0004</t>
+  </si>
+  <si>
     <t>U12M</t>
   </si>
   <si>
+    <t>1110</t>
+  </si>
+  <si>
+    <t>BDRK_R0012</t>
+  </si>
+  <si>
     <t>U13H</t>
   </si>
   <si>
+    <t>1120</t>
+  </si>
+  <si>
+    <t>BDRK_R0017</t>
+  </si>
+  <si>
     <t>U14H</t>
   </si>
   <si>
+    <t>1130</t>
+  </si>
+  <si>
+    <t>BDRK_R0015</t>
+  </si>
+  <si>
     <t>U15H</t>
   </si>
   <si>
+    <t>1140</t>
+  </si>
+  <si>
+    <t>BDRK_R0002</t>
+  </si>
+  <si>
     <t>U16M</t>
   </si>
   <si>
+    <t>1150</t>
+  </si>
+  <si>
+    <t>BDRK_R0011</t>
+  </si>
+  <si>
     <t>U17H</t>
   </si>
   <si>
+    <t>1160</t>
+  </si>
+  <si>
+    <t>BDRK_R0001</t>
+  </si>
+  <si>
     <t>U18H</t>
   </si>
   <si>
+    <t>1170</t>
+  </si>
+  <si>
+    <t>BDRK_R0008</t>
+  </si>
+  <si>
     <t>U19M</t>
   </si>
   <si>
+    <t>1180</t>
+  </si>
+  <si>
+    <t>BDRK_R0006</t>
+  </si>
+  <si>
     <t>C20M</t>
   </si>
   <si>
+    <t>1190</t>
+  </si>
+  <si>
+    <t>sample_ID</t>
+  </si>
+  <si>
+    <t>sample_name</t>
+  </si>
+  <si>
     <t>site</t>
+  </si>
+  <si>
+    <t>date_text_PST</t>
+  </si>
+  <si>
+    <t>time_text_PST</t>
+  </si>
+  <si>
+    <t>BDRK_B01M_GB_20260727_1000</t>
+  </si>
+  <si>
+    <t>BDRK_B02H_GB_20260727_1010</t>
+  </si>
+  <si>
+    <t>BDRK_B03H_GB_20260727_1020</t>
+  </si>
+  <si>
+    <t>BDRK_B04M_GB_20260727_1030</t>
+  </si>
+  <si>
+    <t>BDRK_B05H_GB_20260727_1040</t>
+  </si>
+  <si>
+    <t>BDRK_B06H_GB_20260727_1050</t>
+  </si>
+  <si>
+    <t>BDRK_B07H_GB_20260727_1060</t>
+  </si>
+  <si>
+    <t>BDRK_B08M_GB_20260727_1070</t>
+  </si>
+  <si>
+    <t>BDRK_B09H_GB_20260727_1080</t>
+  </si>
+  <si>
+    <t>BDRK_B10M_GB_20260727_1090</t>
+  </si>
+  <si>
+    <t>BDRK_U11H_GB_20260727_1100</t>
+  </si>
+  <si>
+    <t>BDRK_U12M_GB_20260727_1110</t>
+  </si>
+  <si>
+    <t>BDRK_U13H_GB_20260727_1120</t>
+  </si>
+  <si>
+    <t>BDRK_U14H_GB_20260727_1130</t>
+  </si>
+  <si>
+    <t>BDRK_U15H_GB_20260727_1140</t>
+  </si>
+  <si>
+    <t>BDRK_U16M_GB_20260727_1150</t>
+  </si>
+  <si>
+    <t>BDRK_U17H_GB_20260727_1160</t>
+  </si>
+  <si>
+    <t>BDRK_U18H_GB_20260727_1170</t>
+  </si>
+  <si>
+    <t>BDRK_U19M_GB_20260727_1180</t>
+  </si>
+  <si>
+    <t>BDRK_C20M_GB_20260727_1190</t>
+  </si>
+  <si>
+    <t>BDRK_U18H_GB_20260727_1170_CN</t>
+  </si>
+  <si>
+    <t>Shimadzu</t>
+  </si>
+  <si>
+    <t>BDRK_U18H_GB_20260727_1170_AQ</t>
+  </si>
+  <si>
+    <t>Aqualog</t>
+  </si>
+  <si>
+    <t>BDRK_U18H_GB_20260727_1170_NU</t>
+  </si>
+  <si>
+    <t>CCAL</t>
+  </si>
+  <si>
+    <t>BDRK_U18H_GB_20260727_1170_EX</t>
+  </si>
+  <si>
+    <t>Excess</t>
+  </si>
+  <si>
+    <t>BDRK_U18H_GB_20260727_1170_LV</t>
+  </si>
+  <si>
+    <t>Levoglucosan</t>
+  </si>
+  <si>
+    <t>BDRK_U16M_GB_20260727_1150_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U16M_GB_20260727_1150_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U16M_GB_20260727_1150_NU</t>
+  </si>
+  <si>
+    <t>BDRK_U16M_GB_20260727_1150_EX</t>
+  </si>
+  <si>
+    <t>BDRK_U16M_GB_20260727_1150_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B06H_GB_20260727_1050_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B06H_GB_20260727_1050_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B06H_GB_20260727_1050_NU</t>
+  </si>
+  <si>
+    <t>BDRK_B06H_GB_20260727_1050_EX</t>
+  </si>
+  <si>
+    <t>BDRK_B06H_GB_20260727_1050_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U12M_GB_20260727_1110_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U12M_GB_20260727_1110_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U12M_GB_20260727_1110_NU</t>
+  </si>
+  <si>
+    <t>BDRK_U12M_GB_20260727_1110_EX</t>
+  </si>
+  <si>
+    <t>BDRK_U12M_GB_20260727_1110_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U11H_GB_20260727_1100_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U11H_GB_20260727_1100_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U11H_GB_20260727_1100_NU</t>
+  </si>
+  <si>
+    <t>BDRK_U11H_GB_20260727_1100_EX</t>
+  </si>
+  <si>
+    <t>BDRK_U11H_GB_20260727_1100_LV</t>
+  </si>
+  <si>
+    <t>BDRK_C20M_GB_20260727_1190_CN</t>
+  </si>
+  <si>
+    <t>BDRK_C20M_GB_20260727_1190_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_C20M_GB_20260727_1190_NU</t>
+  </si>
+  <si>
+    <t>BDRK_C20M_GB_20260727_1190_EX</t>
+  </si>
+  <si>
+    <t>BDRK_C20M_GB_20260727_1190_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B07H_GB_20260727_1060_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B07H_GB_20260727_1060_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B07H_GB_20260727_1060_NU</t>
+  </si>
+  <si>
+    <t>BDRK_B07H_GB_20260727_1060_EX</t>
+  </si>
+  <si>
+    <t>BDRK_B07H_GB_20260727_1060_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U19M_GB_20260727_1180_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U19M_GB_20260727_1180_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U19M_GB_20260727_1180_NU</t>
+  </si>
+  <si>
+    <t>BDRK_U19M_GB_20260727_1180_EX</t>
+  </si>
+  <si>
+    <t>BDRK_U19M_GB_20260727_1180_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B03H_GB_20260727_1020_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B03H_GB_20260727_1020_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B03H_GB_20260727_1020_NU</t>
+  </si>
+  <si>
+    <t>BDRK_B03H_GB_20260727_1020_EX</t>
+  </si>
+  <si>
+    <t>BDRK_B03H_GB_20260727_1020_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B10M_GB_20260727_1090_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B10M_GB_20260727_1090_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B10M_GB_20260727_1090_NU</t>
+  </si>
+  <si>
+    <t>BDRK_B10M_GB_20260727_1090_EX</t>
+  </si>
+  <si>
+    <t>BDRK_B10M_GB_20260727_1090_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U17H_GB_20260727_1160_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U17H_GB_20260727_1160_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U17H_GB_20260727_1160_NU</t>
+  </si>
+  <si>
+    <t>BDRK_U17H_GB_20260727_1160_EX</t>
+  </si>
+  <si>
+    <t>BDRK_U17H_GB_20260727_1160_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U13H_GB_20260727_1120_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U13H_GB_20260727_1120_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U13H_GB_20260727_1120_NU</t>
+  </si>
+  <si>
+    <t>BDRK_U13H_GB_20260727_1120_EX</t>
+  </si>
+  <si>
+    <t>BDRK_U13H_GB_20260727_1120_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B08M_GB_20260727_1070_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B08M_GB_20260727_1070_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B08M_GB_20260727_1070_NU</t>
+  </si>
+  <si>
+    <t>BDRK_B08M_GB_20260727_1070_EX</t>
+  </si>
+  <si>
+    <t>BDRK_B08M_GB_20260727_1070_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B09H_GB_20260727_1080_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B09H_GB_20260727_1080_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B09H_GB_20260727_1080_NU</t>
+  </si>
+  <si>
+    <t>BDRK_B09H_GB_20260727_1080_EX</t>
+  </si>
+  <si>
+    <t>BDRK_B09H_GB_20260727_1080_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U15H_GB_20260727_1140_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U15H_GB_20260727_1140_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U15H_GB_20260727_1140_NU</t>
+  </si>
+  <si>
+    <t>BDRK_U15H_GB_20260727_1140_EX</t>
+  </si>
+  <si>
+    <t>BDRK_U15H_GB_20260727_1140_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B02H_GB_20260727_1010_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B02H_GB_20260727_1010_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B02H_GB_20260727_1010_NU</t>
+  </si>
+  <si>
+    <t>BDRK_B02H_GB_20260727_1010_EX</t>
+  </si>
+  <si>
+    <t>BDRK_B02H_GB_20260727_1010_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U14H_GB_20260727_1130_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U14H_GB_20260727_1130_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U14H_GB_20260727_1130_NU</t>
+  </si>
+  <si>
+    <t>BDRK_U14H_GB_20260727_1130_EX</t>
+  </si>
+  <si>
+    <t>BDRK_U14H_GB_20260727_1130_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B01M_GB_20260727_1000_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B01M_GB_20260727_1000_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B01M_GB_20260727_1000_NU</t>
+  </si>
+  <si>
+    <t>BDRK_B01M_GB_20260727_1000_EX</t>
+  </si>
+  <si>
+    <t>BDRK_B01M_GB_20260727_1000_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B05H_GB_20260727_1040_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B05H_GB_20260727_1040_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B05H_GB_20260727_1040_NU</t>
+  </si>
+  <si>
+    <t>BDRK_B05H_GB_20260727_1040_EX</t>
+  </si>
+  <si>
+    <t>BDRK_B05H_GB_20260727_1040_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B04M_GB_20260727_1030_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B04M_GB_20260727_1030_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B04M_GB_20260727_1030_NU</t>
+  </si>
+  <si>
+    <t>BDRK_B04M_GB_20260727_1030_EX</t>
+  </si>
+  <si>
+    <t>BDRK_B04M_GB_20260727_1030_LV</t>
   </si>
 </sst>
 </file>
@@ -257,7 +743,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -286,12 +772,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
         <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -395,7 +875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -431,22 +911,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1044,12 +1518,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18E7393F-7780-4CE5-9226-E771755C3838}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.453125" customWidth="1"/>
-    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.453125" customWidth="1"/>
     <col min="4" max="4" width="18.1796875" style="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.7265625" style="15" bestFit="1" customWidth="1"/>
@@ -1057,119 +1531,359 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="D1" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
         <v>24</v>
       </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>60</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
       <c r="C16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
       <c r="C17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
       <c r="C18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
       <c r="C19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
       <c r="C20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>78</v>
+      </c>
+      <c r="D21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1230,20 +1944,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4412F0D1-F35D-46A9-AB3E-79F4F5A54491}">
-  <dimension ref="A1:B1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.7265625" customWidth="1"/>
     <col min="2" max="2" width="36.7265625" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1278,27 +1996,1127 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59BE4EE-0A7A-4560-B9C6-822B0B7C8D4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>136</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>140</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>141</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>142</v>
+      </c>
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>143</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>144</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>146</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>147</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>149</v>
+      </c>
+      <c r="B41" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>153</v>
+      </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>154</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>155</v>
+      </c>
+      <c r="B47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>156</v>
+      </c>
+      <c r="B48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>157</v>
+      </c>
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>158</v>
+      </c>
+      <c r="B50" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>159</v>
+      </c>
+      <c r="B51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>160</v>
+      </c>
+      <c r="B52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>163</v>
+      </c>
+      <c r="B55" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>164</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>165</v>
+      </c>
+      <c r="B57" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>166</v>
+      </c>
+      <c r="B58" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>167</v>
+      </c>
+      <c r="B59" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>168</v>
+      </c>
+      <c r="B60" t="s">
+        <v>56</v>
+      </c>
+      <c r="C60" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>169</v>
+      </c>
+      <c r="B61" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>170</v>
+      </c>
+      <c r="B62" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>171</v>
+      </c>
+      <c r="B63" t="s">
+        <v>41</v>
+      </c>
+      <c r="C63" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>172</v>
+      </c>
+      <c r="B64" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>173</v>
+      </c>
+      <c r="B65" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>174</v>
+      </c>
+      <c r="B66" t="s">
+        <v>41</v>
+      </c>
+      <c r="C66" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>175</v>
+      </c>
+      <c r="B67" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>176</v>
+      </c>
+      <c r="B68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C68" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>177</v>
+      </c>
+      <c r="B69" t="s">
+        <v>44</v>
+      </c>
+      <c r="C69" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>178</v>
+      </c>
+      <c r="B70" t="s">
+        <v>44</v>
+      </c>
+      <c r="C70" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>179</v>
+      </c>
+      <c r="B71" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>180</v>
+      </c>
+      <c r="B72" t="s">
+        <v>62</v>
+      </c>
+      <c r="C72" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>181</v>
+      </c>
+      <c r="B73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C73" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>182</v>
+      </c>
+      <c r="B74" t="s">
+        <v>62</v>
+      </c>
+      <c r="C74" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>183</v>
+      </c>
+      <c r="B75" t="s">
+        <v>62</v>
+      </c>
+      <c r="C75" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>184</v>
+      </c>
+      <c r="B76" t="s">
+        <v>62</v>
+      </c>
+      <c r="C76" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>185</v>
+      </c>
+      <c r="B77" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>186</v>
+      </c>
+      <c r="B78" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>187</v>
+      </c>
+      <c r="B79" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>188</v>
+      </c>
+      <c r="B80" t="s">
+        <v>23</v>
+      </c>
+      <c r="C80" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>189</v>
+      </c>
+      <c r="B81" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>190</v>
+      </c>
+      <c r="B82" t="s">
+        <v>59</v>
+      </c>
+      <c r="C82" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>191</v>
+      </c>
+      <c r="B83" t="s">
+        <v>59</v>
+      </c>
+      <c r="C83" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>192</v>
+      </c>
+      <c r="B84" t="s">
+        <v>59</v>
+      </c>
+      <c r="C84" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>193</v>
+      </c>
+      <c r="B85" t="s">
+        <v>59</v>
+      </c>
+      <c r="C85" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>194</v>
+      </c>
+      <c r="B86" t="s">
+        <v>59</v>
+      </c>
+      <c r="C86" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>195</v>
+      </c>
+      <c r="B87" t="s">
+        <v>19</v>
+      </c>
+      <c r="C87" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>196</v>
+      </c>
+      <c r="B88" t="s">
+        <v>19</v>
+      </c>
+      <c r="C88" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>197</v>
+      </c>
+      <c r="B89" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>198</v>
+      </c>
+      <c r="B90" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>199</v>
+      </c>
+      <c r="B91" t="s">
+        <v>19</v>
+      </c>
+      <c r="C91" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>200</v>
+      </c>
+      <c r="B92" t="s">
+        <v>32</v>
+      </c>
+      <c r="C92" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>201</v>
+      </c>
+      <c r="B93" t="s">
+        <v>32</v>
+      </c>
+      <c r="C93" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>202</v>
+      </c>
+      <c r="B94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C94" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>203</v>
+      </c>
+      <c r="B95" t="s">
+        <v>32</v>
+      </c>
+      <c r="C95" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>204</v>
+      </c>
+      <c r="B96" t="s">
+        <v>32</v>
+      </c>
+      <c r="C96" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>205</v>
+      </c>
+      <c r="B97" t="s">
+        <v>29</v>
+      </c>
+      <c r="C97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>206</v>
+      </c>
+      <c r="B98" t="s">
+        <v>29</v>
+      </c>
+      <c r="C98" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>207</v>
+      </c>
+      <c r="B99" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>208</v>
+      </c>
+      <c r="B100" t="s">
+        <v>29</v>
+      </c>
+      <c r="C100" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>209</v>
+      </c>
+      <c r="B101" t="s">
+        <v>29</v>
+      </c>
+      <c r="C101" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1350,8 +3168,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="86" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
+  <pageSetup scale="86" fitToHeight="0" orientation="landscape"/>
+  <headerFooter scaleWithDoc="0" alignWithMargins="0">
     <oddHeader>&amp;L&amp;"Consolas,Bold"&amp;13Date:____________________ Technican:___________________ 
 Project Code:___________  Study Code:_____________</oddHeader>
     <oddFooter>&amp;C&amp;"Consolas,Regular"&amp;14&amp;P of &amp;N</oddFooter>
@@ -1360,7 +3178,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{363C61CB-AFF6-4988-8C26-F70360C91095}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1375,171 +3193,251 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="18"/>
+      <c r="A1" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="20"/>
       <c r="E1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="10"/>
+      <c r="A3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>102</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>100</v>
+      </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="10"/>
+      <c r="A5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>90</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>96</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="10"/>
+      <c r="A7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>95</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>104</v>
+      </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="10"/>
+      <c r="A9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>91</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="B10" s="11"/>
+      <c r="A10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>103</v>
+      </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="10"/>
+      <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>87</v>
+      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>94</v>
+      </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="10"/>
+      <c r="A13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3"/>
-      <c r="B14" s="11"/>
+      <c r="A14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>97</v>
+      </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="10"/>
+      <c r="A15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3"/>
-      <c r="B16" s="11"/>
+      <c r="A16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>93</v>
+      </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
-      <c r="B17" s="10"/>
+      <c r="A17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>99</v>
+      </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="3"/>
-      <c r="B18" s="11"/>
+      <c r="A18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>86</v>
+      </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-      <c r="B19" s="10"/>
+      <c r="A19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>98</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="3"/>
-      <c r="B20" s="11"/>
+      <c r="A20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>85</v>
+      </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="10"/>
+      <c r="A21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>89</v>
+      </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="3"/>
-      <c r="B22" s="11"/>
+      <c r="A22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>88</v>
+      </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -2089,8 +3987,8 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="99" fitToHeight="0" orientation="portrait" r:id="rId1"/>
-  <headerFooter>
+  <pageSetup scale="99" fitToHeight="0" orientation="portrait"/>
+  <headerFooter scaleWithDoc="0" alignWithMargins="0">
     <oddHeader>&amp;L&amp;"Consolas,Bold"&amp;12Date:____________________ Technican:___________________ 
 Project Code:___________  Study Code:_____________</oddHeader>
     <oddFooter>&amp;C&amp;"Consolas,Bold"&amp;14&amp;P of &amp;N</oddFooter>
@@ -2099,7 +3997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C94F4C7-78F1-4C98-B28B-4E3D6C123D4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2116,10 +4014,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="18"/>
       <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
@@ -2138,30 +4036,34 @@
     </row>
     <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="3" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="10"/>
+      <c r="A3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>102</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2169,8 +4071,12 @@
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>100</v>
+      </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -2178,8 +4084,12 @@
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>90</v>
+      </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -2187,8 +4097,12 @@
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>96</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -2196,8 +4110,12 @@
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="4"/>
-      <c r="B7" s="12"/>
+      <c r="A7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>95</v>
+      </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -2205,8 +4123,12 @@
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>104</v>
+      </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -2214,8 +4136,12 @@
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="4"/>
-      <c r="B9" s="12"/>
+      <c r="A9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>91</v>
+      </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -2223,8 +4149,12 @@
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="B10" s="11"/>
+      <c r="A10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>103</v>
+      </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -2232,8 +4162,12 @@
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="4"/>
-      <c r="B11" s="12"/>
+      <c r="A11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>87</v>
+      </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -2241,8 +4175,12 @@
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>94</v>
+      </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -2250,8 +4188,12 @@
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="4"/>
-      <c r="B13" s="12"/>
+      <c r="A13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>101</v>
+      </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -2259,8 +4201,12 @@
       <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3"/>
-      <c r="B14" s="11"/>
+      <c r="A14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>97</v>
+      </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -2268,8 +4214,12 @@
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="4"/>
-      <c r="B15" s="12"/>
+      <c r="A15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -2277,8 +4227,12 @@
       <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3"/>
-      <c r="B16" s="11"/>
+      <c r="A16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>93</v>
+      </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -2286,8 +4240,12 @@
       <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="4"/>
-      <c r="B17" s="12"/>
+      <c r="A17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>99</v>
+      </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -2295,8 +4253,12 @@
       <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="3"/>
-      <c r="B18" s="11"/>
+      <c r="A18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>86</v>
+      </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -2304,8 +4266,12 @@
       <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="4"/>
-      <c r="B19" s="12"/>
+      <c r="A19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -2313,8 +4279,12 @@
       <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="3"/>
-      <c r="B20" s="11"/>
+      <c r="A20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>85</v>
+      </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -2322,8 +4292,12 @@
       <c r="G20" s="3"/>
     </row>
     <row r="21" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="4"/>
-      <c r="B21" s="12"/>
+      <c r="A21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>89</v>
+      </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -2331,8 +4305,12 @@
       <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="3"/>
-      <c r="B22" s="11"/>
+      <c r="A22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>88</v>
+      </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -2992,747 +4970,8 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="95" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;"Consolas,Bold"&amp;12Date:____________________ Technican:___________________ 
-Project Code:___________  Study Code:_____________</oddHeader>
-    <oddFooter>&amp;C&amp;"Consolas,Bold"&amp;14&amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B79AE67-9E12-4923-915F-252B25B4802C}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.453125" customWidth="1"/>
-    <col min="2" max="2" width="29.7265625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" customWidth="1"/>
-    <col min="5" max="5" width="36" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="3"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="3"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="3"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="3"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="3"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="3"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="2"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="3"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="2"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="3"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="2"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="3"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-    </row>
-    <row r="35" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="2"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="3"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-    </row>
-    <row r="37" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="2"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="3"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-    </row>
-    <row r="39" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="2"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="3"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-    </row>
-    <row r="41" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="2"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-    </row>
-    <row r="42" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="3"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-    </row>
-    <row r="43" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="2"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-    </row>
-    <row r="44" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="3"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="2"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-    </row>
-    <row r="46" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="3"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-    </row>
-    <row r="47" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="2"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-    </row>
-    <row r="48" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="3"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="2"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-    </row>
-    <row r="50" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="3"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="2"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-    </row>
-    <row r="52" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="3"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="2"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-    </row>
-    <row r="54" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="3"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-    </row>
-    <row r="55" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="2"/>
-      <c r="B55" s="10"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-    </row>
-    <row r="56" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="3"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-    </row>
-    <row r="57" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="2"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-    </row>
-    <row r="58" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="3"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-    </row>
-    <row r="59" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="2"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-    </row>
-    <row r="60" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="3"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-    </row>
-    <row r="61" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="2"/>
-      <c r="B61" s="10"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-    </row>
-    <row r="62" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A62" s="3"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-    </row>
-    <row r="63" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="2"/>
-      <c r="B63" s="10"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-    </row>
-    <row r="64" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A64" s="3"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-    </row>
-    <row r="65" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A65" s="2"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-    </row>
-    <row r="66" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A66" s="3"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-    </row>
-    <row r="67" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="2"/>
-      <c r="B67" s="10"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-    </row>
-    <row r="68" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A68" s="3"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-    </row>
-    <row r="69" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A69" s="2"/>
-      <c r="B69" s="10"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-    </row>
-    <row r="70" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A70" s="3"/>
-      <c r="B70" s="11"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-    </row>
-    <row r="71" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="2"/>
-      <c r="B71" s="10"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-    </row>
-    <row r="72" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="3"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-    </row>
-    <row r="73" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A73" s="2"/>
-      <c r="B73" s="10"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-    </row>
-    <row r="74" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A74" s="3"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-    </row>
-    <row r="75" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A75" s="2"/>
-      <c r="B75" s="10"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-    </row>
-    <row r="76" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A76" s="3"/>
-      <c r="B76" s="11"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-    </row>
-    <row r="77" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A77" s="2"/>
-      <c r="B77" s="10"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-    </row>
-    <row r="78" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A78" s="3"/>
-      <c r="B78" s="11"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-    </row>
-    <row r="79" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="2"/>
-      <c r="B79" s="10"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-    </row>
-    <row r="80" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A80" s="3"/>
-      <c r="B80" s="11"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-    </row>
-    <row r="81" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A81" s="2"/>
-      <c r="B81" s="10"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A82" s="3"/>
-      <c r="B82" s="11"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-    </row>
-    <row r="83" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A83" s="2"/>
-      <c r="B83" s="10"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-    </row>
-    <row r="84" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A84" s="3"/>
-      <c r="B84" s="11"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-    </row>
-    <row r="85" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A85" s="2"/>
-      <c r="B85" s="10"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-    </row>
-    <row r="86" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A86" s="3"/>
-      <c r="B86" s="11"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-    </row>
-    <row r="87" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A87" s="2"/>
-      <c r="B87" s="10"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-    </row>
-    <row r="88" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A88" s="3"/>
-      <c r="B88" s="11"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-    </row>
-    <row r="89" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A89" s="2"/>
-      <c r="B89" s="10"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-    </row>
-    <row r="90" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A90" s="3"/>
-      <c r="B90" s="11"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-    </row>
-    <row r="91" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A91" s="2"/>
-      <c r="B91" s="10"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-    </row>
-    <row r="92" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A92" s="3"/>
-      <c r="B92" s="11"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-    </row>
-    <row r="93" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A93" s="2"/>
-      <c r="B93" s="10"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-    </row>
-    <row r="94" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A94" s="3"/>
-      <c r="B94" s="11"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-    </row>
-    <row r="95" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A95" s="2"/>
-      <c r="B95" s="10"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-    </row>
-    <row r="96" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A96" s="3"/>
-      <c r="B96" s="11"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-    </row>
-    <row r="97" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A97" s="2"/>
-      <c r="B97" s="10"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-    </row>
-    <row r="98" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A98" s="3"/>
-      <c r="B98" s="11"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-    </row>
-    <row r="99" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A99" s="2"/>
-      <c r="B99" s="10"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="98" fitToHeight="0" orientation="portrait" r:id="rId1"/>
-  <headerFooter>
+  <pageSetup scale="95" fitToHeight="0" orientation="landscape"/>
+  <headerFooter scaleWithDoc="0" alignWithMargins="0">
     <oddHeader>&amp;L&amp;"Consolas,Bold"&amp;12Date:____________________ Technican:___________________ 
 Project Code:___________  Study Code:_____________</oddHeader>
     <oddFooter>&amp;C&amp;"Consolas,Bold"&amp;14&amp;P of &amp;N</oddFooter>
